--- a/bitacora_web_avance/plantilla/plantillaInec.xlsx
+++ b/bitacora_web_avance/plantilla/plantillaInec.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AWII\login-portuaria-v1\bitacora_web_avance\plantilla\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A51D67ED-62D1-4BD8-8C85-D244766C0DD7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F3511FC-6E5D-4EC0-8820-23FAB414D030}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{F08222EA-459A-4EBF-AF1A-4C6700C433A0}"/>
   </bookViews>
@@ -196,7 +196,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -228,19 +228,6 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -276,20 +263,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -798,15 +785,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>445524</xdr:colOff>
+      <xdr:colOff>675042</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>11476</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>626431</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>138266</xdr:rowOff>
+      <xdr:colOff>504940</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>16325</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -835,8 +822,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="445524" y="0"/>
-          <a:ext cx="1194859" cy="1106129"/>
+          <a:off x="675042" y="11476"/>
+          <a:ext cx="851253" cy="796686"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -849,33 +836,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E7ED3E3B-1F6F-4789-8109-F8B959D0A1CA}" name="Tabla3" displayName="Tabla3" ref="A8:X36" totalsRowShown="0" headerRowDxfId="26" dataDxfId="0" headerRowBorderDxfId="25" dataCellStyle="Celda de comprobación">
-  <autoFilter ref="A8:X36" xr:uid="{E7ED3E3B-1F6F-4789-8109-F8B959D0A1CA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{E7ED3E3B-1F6F-4789-8109-F8B959D0A1CA}" name="Tabla3" displayName="Tabla3" ref="A8:X9" totalsRowShown="0" headerRowDxfId="26" dataDxfId="24" headerRowBorderDxfId="25" dataCellStyle="Celda de comprobación">
+  <autoFilter ref="A8:X9" xr:uid="{E7ED3E3B-1F6F-4789-8109-F8B959D0A1CA}"/>
   <tableColumns count="24">
-    <tableColumn id="1" xr3:uid="{D2F32DF9-BC28-4AEC-99EF-3FF9F82C3DC5}" name="idregistro" dataDxfId="24" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="2" xr3:uid="{D2776CA0-4BCE-4915-93C6-4E375F9C9CE5}" name="idbuque" dataDxfId="23" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="3" xr3:uid="{7B55283D-90F9-48FD-B43E-286CB13A8F01}" name="matricula" dataDxfId="22" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="4" xr3:uid="{3A158A7A-E7A0-4BA1-86A0-3363CA484A2A}" name="buque" dataDxfId="21" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="5" xr3:uid="{0EB9E5E9-7BF1-44BC-9E98-E40EF1F32C80}" name="tipo_nave" dataDxfId="20" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="6" xr3:uid="{BA3F63BC-A7DE-499B-A150-41FE2CACBB45}" name="trafico" dataDxfId="19" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="7" xr3:uid="{025E5A5C-A3E0-4C73-A1CD-90230278F2FE}" name="arribo " dataDxfId="18" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="8" xr3:uid="{D06F5181-8A9F-405C-ACF6-2649047F2BDB}" name="zarpe" dataDxfId="17" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="9" xr3:uid="{585714EB-1C3E-4CEF-92BE-87C30C84C5CC}" name="bandera" dataDxfId="16" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="10" xr3:uid="{BF627498-5147-4522-9910-CEF1073E89FB}" name="TRB" dataDxfId="15" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="11" xr3:uid="{0D6CADC5-AA87-475C-8CC2-BD764BDBD8A8}" name="TRN" dataDxfId="14" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="12" xr3:uid="{DD9E897E-5B00-4B4B-B92C-1AA2A20E1129}" name="Pasajeros_e" dataDxfId="13" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="13" xr3:uid="{0CD67C48-3068-49A2-AA41-576AC0F7E890}" name="Pasajeros_s" dataDxfId="12" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="14" xr3:uid="{25E58D18-FB35-47C3-AB6D-DF7D60C81245}" name="agencia" dataDxfId="11" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="15" xr3:uid="{C0688010-54A5-41C1-9490-08B5EBDE1017}" name="Eslora" dataDxfId="10" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="16" xr3:uid="{1A4F8580-3D17-48C9-A46E-034A01DEEAD6}" name="Calado" dataDxfId="9" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="17" xr3:uid="{7009D877-2CB5-4A1B-BDD8-3E3D3426D00C}" name="tipo_contrato" dataDxfId="8" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="18" xr3:uid="{8948463F-839C-4E52-8015-A3FBB27EE179}" name="p_bruto" dataDxfId="7" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="19" xr3:uid="{6321DF37-38B4-4C33-8532-D3AC175713CA}" name="p_neto" dataDxfId="6" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="20" xr3:uid="{9EE2D342-FDB1-4C8C-9615-386C4679CF3D}" name="estado" dataDxfId="5" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="21" xr3:uid="{5257867B-E196-49E5-AF07-6F2FF3A833AA}" name="usuario" dataDxfId="4" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="22" xr3:uid="{78ED5CD3-A929-4088-BD80-BF768BCB39C5}" name="scregistro" dataDxfId="3" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="23" xr3:uid="{D3281BE1-281A-49E8-B36D-D1C53FF63EAE}" name="mes" dataDxfId="2" dataCellStyle="Celda de comprobación"/>
-    <tableColumn id="24" xr3:uid="{EC58454C-EF9E-4E36-BDC7-72D1D6CC91D9}" name="tonelada" dataDxfId="1" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="1" xr3:uid="{D2F32DF9-BC28-4AEC-99EF-3FF9F82C3DC5}" name="idregistro" dataDxfId="23" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="2" xr3:uid="{D2776CA0-4BCE-4915-93C6-4E375F9C9CE5}" name="idbuque" dataDxfId="22" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="3" xr3:uid="{7B55283D-90F9-48FD-B43E-286CB13A8F01}" name="matricula" dataDxfId="21" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="4" xr3:uid="{3A158A7A-E7A0-4BA1-86A0-3363CA484A2A}" name="buque" dataDxfId="20" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="5" xr3:uid="{0EB9E5E9-7BF1-44BC-9E98-E40EF1F32C80}" name="tipo_nave" dataDxfId="19" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="6" xr3:uid="{BA3F63BC-A7DE-499B-A150-41FE2CACBB45}" name="trafico" dataDxfId="18" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="7" xr3:uid="{025E5A5C-A3E0-4C73-A1CD-90230278F2FE}" name="arribo " dataDxfId="17" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="8" xr3:uid="{D06F5181-8A9F-405C-ACF6-2649047F2BDB}" name="zarpe" dataDxfId="16" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="9" xr3:uid="{585714EB-1C3E-4CEF-92BE-87C30C84C5CC}" name="bandera" dataDxfId="15" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="10" xr3:uid="{BF627498-5147-4522-9910-CEF1073E89FB}" name="TRB" dataDxfId="14" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="11" xr3:uid="{0D6CADC5-AA87-475C-8CC2-BD764BDBD8A8}" name="TRN" dataDxfId="13" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="12" xr3:uid="{DD9E897E-5B00-4B4B-B92C-1AA2A20E1129}" name="Pasajeros_e" dataDxfId="12" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="13" xr3:uid="{0CD67C48-3068-49A2-AA41-576AC0F7E890}" name="Pasajeros_s" dataDxfId="11" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="14" xr3:uid="{25E58D18-FB35-47C3-AB6D-DF7D60C81245}" name="agencia" dataDxfId="10" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="15" xr3:uid="{C0688010-54A5-41C1-9490-08B5EBDE1017}" name="Eslora" dataDxfId="9" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="16" xr3:uid="{1A4F8580-3D17-48C9-A46E-034A01DEEAD6}" name="Calado" dataDxfId="8" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="17" xr3:uid="{7009D877-2CB5-4A1B-BDD8-3E3D3426D00C}" name="tipo_contrato" dataDxfId="7" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="18" xr3:uid="{8948463F-839C-4E52-8015-A3FBB27EE179}" name="p_bruto" dataDxfId="6" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="19" xr3:uid="{6321DF37-38B4-4C33-8532-D3AC175713CA}" name="p_neto" dataDxfId="5" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="20" xr3:uid="{9EE2D342-FDB1-4C8C-9615-386C4679CF3D}" name="estado" dataDxfId="4" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="21" xr3:uid="{5257867B-E196-49E5-AF07-6F2FF3A833AA}" name="usuario" dataDxfId="3" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="22" xr3:uid="{78ED5CD3-A929-4088-BD80-BF768BCB39C5}" name="scregistro" dataDxfId="2" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="23" xr3:uid="{D3281BE1-281A-49E8-B36D-D1C53FF63EAE}" name="mes" dataDxfId="1" dataCellStyle="Celda de comprobación"/>
+    <tableColumn id="24" xr3:uid="{EC58454C-EF9E-4E36-BDC7-72D1D6CC91D9}" name="tonelada" dataDxfId="0" dataCellStyle="Celda de comprobación"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1178,7 +1165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2190310D-A596-457F-8ABA-D9A5B7AC8B7C}">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" style="2" customWidth="1"/>
@@ -1312,7 +1299,11 @@
       <c r="B6" s="14"/>
       <c r="C6" s="14"/>
     </row>
-    <row r="7" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+    </row>
     <row r="8" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>3</v>
@@ -1413,709 +1404,7 @@
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
     </row>
-    <row r="10" spans="1:29" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="1"/>
-      <c r="X10" s="1"/>
-    </row>
-    <row r="11" spans="1:29" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="1"/>
-    </row>
-    <row r="12" spans="1:29" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1"/>
-      <c r="W12" s="1"/>
-      <c r="X12" s="1"/>
-    </row>
-    <row r="13" spans="1:29" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="1"/>
-      <c r="W13" s="1"/>
-      <c r="X13" s="1"/>
-    </row>
-    <row r="14" spans="1:29" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
-    </row>
-    <row r="15" spans="1:29" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1"/>
-      <c r="W15" s="1"/>
-      <c r="X15" s="1"/>
-    </row>
-    <row r="16" spans="1:29" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1"/>
-      <c r="X16" s="1"/>
-    </row>
-    <row r="17" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
-      <c r="W17" s="1"/>
-      <c r="X17" s="1"/>
-    </row>
-    <row r="18" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
-      <c r="X18" s="1"/>
-    </row>
-    <row r="19" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="1"/>
-      <c r="X19" s="1"/>
-    </row>
-    <row r="20" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
-      <c r="X20" s="1"/>
-    </row>
-    <row r="21" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
-      <c r="X21" s="1"/>
-    </row>
-    <row r="22" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
-      <c r="W22" s="1"/>
-      <c r="X22" s="1"/>
-    </row>
-    <row r="23" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
-      <c r="W23" s="1"/>
-      <c r="X23" s="1"/>
-    </row>
-    <row r="24" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-      <c r="W24" s="1"/>
-      <c r="X24" s="1"/>
-    </row>
-    <row r="25" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="1"/>
-      <c r="X25" s="1"/>
-    </row>
-    <row r="26" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="1"/>
-      <c r="X26" s="1"/>
-    </row>
-    <row r="27" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="1"/>
-      <c r="X27" s="1"/>
-    </row>
-    <row r="28" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-    </row>
-    <row r="29" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-    </row>
-    <row r="30" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-    </row>
-    <row r="31" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
-      <c r="W31" s="1"/>
-      <c r="X31" s="1"/>
-    </row>
-    <row r="32" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-      <c r="W32" s="1"/>
-      <c r="X32" s="1"/>
-    </row>
-    <row r="33" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
-      <c r="S33" s="1"/>
-      <c r="T33" s="1"/>
-      <c r="U33" s="1"/>
-      <c r="V33" s="1"/>
-      <c r="W33" s="1"/>
-      <c r="X33" s="1"/>
-    </row>
-    <row r="34" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
-      <c r="R34" s="1"/>
-      <c r="S34" s="1"/>
-      <c r="T34" s="1"/>
-      <c r="U34" s="1"/>
-      <c r="V34" s="1"/>
-      <c r="W34" s="1"/>
-      <c r="X34" s="1"/>
-    </row>
-    <row r="35" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
-      <c r="T35" s="1"/>
-      <c r="U35" s="1"/>
-      <c r="V35" s="1"/>
-      <c r="W35" s="1"/>
-      <c r="X35" s="1"/>
-    </row>
-    <row r="36" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="1"/>
-      <c r="S36" s="1"/>
-      <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-      <c r="V36" s="1"/>
-      <c r="W36" s="1"/>
-      <c r="X36" s="1"/>
-    </row>
-    <row r="37" spans="1:24" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:29" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="C3:X3"/>
